--- a/web/files/九龙-启德-天玺．海第2B期.xlsx
+++ b/web/files/九龙-启德-天玺．海第2B期.xlsx
@@ -2034,7 +2034,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -10913,7 +10913,7 @@
           <t>A | 1159呎 (4+房)
 $4870万
 $42,019/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -10921,7 +10921,7 @@
           <t>B | 1157呎 (4+房)
 $4687万
 $40,510/呎
-(26年-07月-20日)</t>
+(26年-07月-21日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr"/>
@@ -10939,7 +10939,7 @@
           <t>A | 1159呎 (4+房)
 $4830万
 $41,674/呎
-(26年-07月-22日)</t>
+(26年-07月-23日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -11017,7 +11017,7 @@
           <t>A | 1159呎 (4+房)
 $5089万
 $43,912/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
